--- a/datasets/weaving/inventory-brightway.xlsx
+++ b/datasets/weaving/inventory-brightway.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vincentcarrieres/carbonfact/lca/lca/notebooks/science/Vincent/Carbonfact database/Weaving/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vincentcarrieres/carbonfact/lca/lca/notebooks/science/Carbonfact database/Weaving/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84F0720F-0659-0F48-8BBF-1489C0D780F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE19F7C-6B81-614C-8BE5-0217CF69FCC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-4540" yWindow="-21000" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,9 +44,6 @@
     <t>Activity</t>
   </si>
   <si>
-    <t>Heat, for dyeing process, production mix</t>
-  </si>
-  <si>
     <t>production amount</t>
   </si>
   <si>
@@ -56,9 +53,6 @@
     <t>reference product</t>
   </si>
   <si>
-    <t>heat, for dyeing process</t>
-  </si>
-  <si>
     <t>location</t>
   </si>
   <si>
@@ -279,6 +273,12 @@
   </si>
   <si>
     <t>market group for tap water</t>
+  </si>
+  <si>
+    <t>Heat, for textile processes, production mix</t>
+  </si>
+  <si>
+    <t>heat, for textile processes</t>
   </si>
 </sst>
 </file>
@@ -649,12 +649,12 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -662,85 +662,85 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
         <v>13</v>
       </c>
-      <c r="B10" t="s">
+      <c r="G10" t="s">
         <v>14</v>
       </c>
-      <c r="C10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="H10" t="s">
         <v>15</v>
       </c>
-      <c r="G10" t="s">
-        <v>16</v>
-      </c>
-      <c r="H10" t="s">
-        <v>17</v>
-      </c>
       <c r="I10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>7</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" t="s">
         <v>9</v>
       </c>
-      <c r="E11" t="s">
-        <v>11</v>
-      </c>
       <c r="G11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H11" t="s">
         <v>1</v>
@@ -748,71 +748,71 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B12">
-        <v>0.47499999999999998</v>
+        <v>0.5</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B13">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B14">
-        <v>0.28499999999999998</v>
+        <v>0.3</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
@@ -820,12 +820,12 @@
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -833,85 +833,85 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
         <v>13</v>
       </c>
-      <c r="B23" t="s">
+      <c r="G23" t="s">
         <v>14</v>
       </c>
-      <c r="C23" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
+      <c r="H23" t="s">
         <v>15</v>
       </c>
-      <c r="G23" t="s">
-        <v>16</v>
-      </c>
-      <c r="H23" t="s">
-        <v>17</v>
-      </c>
       <c r="I23" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" t="s">
         <v>27</v>
       </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" t="s">
-        <v>9</v>
-      </c>
-      <c r="E24" t="s">
-        <v>29</v>
-      </c>
       <c r="G24" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H24" t="s">
         <v>1</v>
@@ -919,45 +919,45 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B25">
         <v>0.201784136</v>
       </c>
       <c r="C25" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D25" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E25" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G25" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H25" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="B26">
         <v>5.3081822689999996</v>
       </c>
       <c r="C26" t="s">
-        <v>7</v>
+        <v>81</v>
       </c>
       <c r="D26" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" t="s">
         <v>9</v>
       </c>
-      <c r="E26" t="s">
-        <v>11</v>
-      </c>
       <c r="G26" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H26" t="s">
         <v>1</v>
@@ -965,186 +965,186 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B27">
         <v>0.102649266</v>
       </c>
       <c r="C27" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D27" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E27" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G27" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H27" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B28">
         <v>8.9260229999999999E-3</v>
       </c>
       <c r="C28" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D28" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E28" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G28" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H28" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B29">
         <v>1.1415445740000001</v>
       </c>
       <c r="C29" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D29" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E29" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G29" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H29" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B30">
         <v>9.4596399999999994E-9</v>
       </c>
       <c r="C30" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D30" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E30" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G30" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H30" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B31">
         <v>-1.4229900000000001E-5</v>
       </c>
       <c r="C31" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D31" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E31" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G31" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H31" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B32">
         <v>5.5781E-5</v>
       </c>
       <c r="C32" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E32" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G32" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H32" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B33">
         <v>-5.3081823E-2</v>
       </c>
       <c r="C33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D33" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E33" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G33" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H33" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B34">
         <v>1.008554631</v>
       </c>
       <c r="D34" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E34" t="s">
+        <v>47</v>
+      </c>
+      <c r="F34" t="s">
         <v>49</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
+        <v>50</v>
+      </c>
+      <c r="H34" t="s">
         <v>51</v>
-      </c>
-      <c r="G34" t="s">
-        <v>52</v>
-      </c>
-      <c r="H34" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
@@ -1152,12 +1152,12 @@
         <v>2</v>
       </c>
       <c r="B36" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -1165,85 +1165,85 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B39" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B41" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
+        <v>11</v>
+      </c>
+      <c r="B43" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" t="s">
+        <v>5</v>
+      </c>
+      <c r="D43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E43" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" t="s">
         <v>13</v>
       </c>
-      <c r="B43" t="s">
+      <c r="G43" t="s">
         <v>14</v>
       </c>
-      <c r="C43" t="s">
-        <v>6</v>
-      </c>
-      <c r="D43" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" t="s">
+      <c r="H43" t="s">
         <v>15</v>
       </c>
-      <c r="G43" t="s">
-        <v>16</v>
-      </c>
-      <c r="H43" t="s">
-        <v>17</v>
-      </c>
       <c r="I43" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B44">
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D44" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E44" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G44" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H44" t="s">
         <v>1</v>
@@ -1251,45 +1251,45 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B45">
         <v>30.255167799999999</v>
       </c>
       <c r="C45" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D45" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E45" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G45" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H45" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B46">
         <v>1.06382979</v>
       </c>
       <c r="C46" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E46" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G46" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H46" t="s">
         <v>1</v>
@@ -1297,117 +1297,117 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B47">
         <v>2.4732529999999999E-2</v>
       </c>
       <c r="C47" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D47" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E47" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G47" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H47" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B48">
         <v>-2.4732529999999999E-2</v>
       </c>
       <c r="C48" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D48" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E48" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G48" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H48" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B49">
         <v>3.9900000000000001E-7</v>
       </c>
       <c r="C49" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D49" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E49" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H49" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B50">
         <v>-1.79721E-3</v>
       </c>
       <c r="C50" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D50" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E50" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B51">
         <v>5.5899999999999997E-5</v>
       </c>
       <c r="C51" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E51" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G51" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H51" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
@@ -1415,12 +1415,12 @@
         <v>2</v>
       </c>
       <c r="B53" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B54">
         <v>1</v>
@@ -1428,85 +1428,85 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B56" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B57" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B58" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
+        <v>11</v>
+      </c>
+      <c r="B60" t="s">
+        <v>12</v>
+      </c>
+      <c r="C60" t="s">
+        <v>5</v>
+      </c>
+      <c r="D60" t="s">
+        <v>6</v>
+      </c>
+      <c r="E60" t="s">
+        <v>8</v>
+      </c>
+      <c r="F60" t="s">
         <v>13</v>
       </c>
-      <c r="B60" t="s">
+      <c r="G60" t="s">
         <v>14</v>
       </c>
-      <c r="C60" t="s">
-        <v>6</v>
-      </c>
-      <c r="D60" t="s">
-        <v>8</v>
-      </c>
-      <c r="E60" t="s">
-        <v>10</v>
-      </c>
-      <c r="F60" t="s">
+      <c r="H60" t="s">
         <v>15</v>
       </c>
-      <c r="G60" t="s">
-        <v>16</v>
-      </c>
-      <c r="H60" t="s">
-        <v>17</v>
-      </c>
       <c r="I60" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B61">
         <v>1</v>
       </c>
       <c r="C61" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E61" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G61" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H61" t="s">
         <v>1</v>
@@ -1514,45 +1514,45 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B62">
         <v>19.753297799999999</v>
       </c>
       <c r="C62" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D62" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E62" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G62" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H62" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B63">
         <v>1.06382979</v>
       </c>
       <c r="C63" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D63" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E63" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G63" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H63" t="s">
         <v>1</v>
@@ -1560,117 +1560,117 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B64">
         <v>2.507417E-2</v>
       </c>
       <c r="C64" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D64" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E64" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G64" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H64" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B65">
         <v>-2.507417E-2</v>
       </c>
       <c r="C65" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D65" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E65" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G65" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H65" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B66">
         <v>4.0499999999999999E-7</v>
       </c>
       <c r="C66" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D66" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E66" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G66" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H66" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B67">
         <v>-1.82204E-3</v>
       </c>
       <c r="C67" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D67" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E67" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G67" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H67" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B68">
         <v>5.6700000000000003E-5</v>
       </c>
       <c r="C68" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D68" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E68" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G68" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H68" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
@@ -1678,12 +1678,12 @@
         <v>2</v>
       </c>
       <c r="B70" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B71">
         <v>1</v>
@@ -1691,85 +1691,85 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B73" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B74" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B75" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
+        <v>11</v>
+      </c>
+      <c r="B77" t="s">
+        <v>12</v>
+      </c>
+      <c r="C77" t="s">
+        <v>5</v>
+      </c>
+      <c r="D77" t="s">
+        <v>6</v>
+      </c>
+      <c r="E77" t="s">
+        <v>8</v>
+      </c>
+      <c r="F77" t="s">
         <v>13</v>
       </c>
-      <c r="B77" t="s">
+      <c r="G77" t="s">
         <v>14</v>
       </c>
-      <c r="C77" t="s">
-        <v>6</v>
-      </c>
-      <c r="D77" t="s">
-        <v>8</v>
-      </c>
-      <c r="E77" t="s">
-        <v>10</v>
-      </c>
-      <c r="F77" t="s">
+      <c r="H77" t="s">
         <v>15</v>
       </c>
-      <c r="G77" t="s">
-        <v>16</v>
-      </c>
-      <c r="H77" t="s">
-        <v>17</v>
-      </c>
       <c r="I77" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B78">
         <v>1</v>
       </c>
       <c r="C78" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D78" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E78" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G78" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H78" t="s">
         <v>1</v>
@@ -1777,45 +1777,45 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B79">
         <v>11.875714800000001</v>
       </c>
       <c r="C79" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D79" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E79" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G79" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H79" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B80">
         <v>1.06382979</v>
       </c>
       <c r="C80" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D80" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E80" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G80" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H80" t="s">
         <v>1</v>
@@ -1823,117 +1823,117 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B81">
         <v>2.578658E-2</v>
       </c>
       <c r="C81" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D81" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E81" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G81" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H81" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B82">
         <v>-2.578658E-2</v>
       </c>
       <c r="C82" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D82" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E82" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G82" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H82" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B83">
         <v>4.1600000000000002E-7</v>
       </c>
       <c r="C83" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D83" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E83" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G83" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H83" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B84">
         <v>-1.8738100000000001E-3</v>
       </c>
       <c r="C84" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D84" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E84" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G84" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H84" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B85">
         <v>5.8300000000000001E-5</v>
       </c>
       <c r="C85" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D85" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E85" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G85" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H85" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
@@ -1941,12 +1941,12 @@
         <v>2</v>
       </c>
       <c r="B87" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B88">
         <v>1</v>
@@ -1954,85 +1954,85 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B90" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B91" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B92" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
+        <v>11</v>
+      </c>
+      <c r="B94" t="s">
+        <v>12</v>
+      </c>
+      <c r="C94" t="s">
+        <v>5</v>
+      </c>
+      <c r="D94" t="s">
+        <v>6</v>
+      </c>
+      <c r="E94" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" t="s">
         <v>13</v>
       </c>
-      <c r="B94" t="s">
+      <c r="G94" t="s">
         <v>14</v>
       </c>
-      <c r="C94" t="s">
-        <v>6</v>
-      </c>
-      <c r="D94" t="s">
-        <v>8</v>
-      </c>
-      <c r="E94" t="s">
-        <v>10</v>
-      </c>
-      <c r="F94" t="s">
+      <c r="H94" t="s">
         <v>15</v>
       </c>
-      <c r="G94" t="s">
-        <v>16</v>
-      </c>
-      <c r="H94" t="s">
-        <v>17</v>
-      </c>
       <c r="I94" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B95">
         <v>1</v>
       </c>
       <c r="C95" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D95" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E95" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G95" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H95" t="s">
         <v>1</v>
@@ -2040,45 +2040,45 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B96">
         <v>9.6739681199999996</v>
       </c>
       <c r="C96" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D96" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E96" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G96" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H96" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B97">
         <v>1.06382979</v>
       </c>
       <c r="C97" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D97" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E97" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G97" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H97" t="s">
         <v>1</v>
@@ -2086,117 +2086,117 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B98">
         <v>2.6233780000000002E-2</v>
       </c>
       <c r="C98" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D98" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E98" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G98" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H98" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B99">
         <v>-2.6233780000000002E-2</v>
       </c>
       <c r="C99" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D99" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E99" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G99" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H99" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B100">
         <v>4.2399999999999999E-7</v>
       </c>
       <c r="C100" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D100" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E100" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G100" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H100" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B101">
         <v>-1.9063000000000001E-3</v>
       </c>
       <c r="C101" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D101" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E101" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G101" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H101" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B102">
         <v>5.9299999999999998E-5</v>
       </c>
       <c r="C102" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D102" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E102" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G102" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H102" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.2">
@@ -2204,12 +2204,12 @@
         <v>2</v>
       </c>
       <c r="B104" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B105">
         <v>1</v>
@@ -2217,85 +2217,85 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B107" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B108" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B109" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
+        <v>11</v>
+      </c>
+      <c r="B111" t="s">
+        <v>12</v>
+      </c>
+      <c r="C111" t="s">
+        <v>5</v>
+      </c>
+      <c r="D111" t="s">
+        <v>6</v>
+      </c>
+      <c r="E111" t="s">
+        <v>8</v>
+      </c>
+      <c r="F111" t="s">
         <v>13</v>
       </c>
-      <c r="B111" t="s">
+      <c r="G111" t="s">
         <v>14</v>
       </c>
-      <c r="C111" t="s">
-        <v>6</v>
-      </c>
-      <c r="D111" t="s">
-        <v>8</v>
-      </c>
-      <c r="E111" t="s">
-        <v>10</v>
-      </c>
-      <c r="F111" t="s">
+      <c r="H111" t="s">
         <v>15</v>
       </c>
-      <c r="G111" t="s">
-        <v>16</v>
-      </c>
-      <c r="H111" t="s">
-        <v>17</v>
-      </c>
       <c r="I111" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B112">
         <v>1</v>
       </c>
       <c r="C112" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D112" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E112" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G112" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H112" t="s">
         <v>1</v>
@@ -2303,45 +2303,45 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B113">
         <v>8.6400229</v>
       </c>
       <c r="C113" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D113" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E113" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G113" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H113" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B114">
         <v>1.06382979</v>
       </c>
       <c r="C114" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D114" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E114" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G114" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H114" t="s">
         <v>1</v>
@@ -2349,117 +2349,117 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B115">
         <v>2.6540640000000001E-2</v>
       </c>
       <c r="C115" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D115" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E115" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G115" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H115" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B116">
         <v>-2.6540640000000001E-2</v>
       </c>
       <c r="C116" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D116" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E116" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G116" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H116" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B117">
         <v>4.2899999999999999E-7</v>
       </c>
       <c r="C117" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D117" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E117" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G117" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H117" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B118">
         <v>-1.9285999999999999E-3</v>
       </c>
       <c r="C118" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D118" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E118" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G118" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H118" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B119">
         <v>6.0000000000000002E-5</v>
       </c>
       <c r="C119" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D119" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E119" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G119" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H119" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.2">
@@ -2467,12 +2467,12 @@
         <v>2</v>
       </c>
       <c r="B121" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -2480,85 +2480,85 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B124" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B125" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B126" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
+        <v>11</v>
+      </c>
+      <c r="B128" t="s">
+        <v>12</v>
+      </c>
+      <c r="C128" t="s">
+        <v>5</v>
+      </c>
+      <c r="D128" t="s">
+        <v>6</v>
+      </c>
+      <c r="E128" t="s">
+        <v>8</v>
+      </c>
+      <c r="F128" t="s">
         <v>13</v>
       </c>
-      <c r="B128" t="s">
+      <c r="G128" t="s">
         <v>14</v>
       </c>
-      <c r="C128" t="s">
-        <v>6</v>
-      </c>
-      <c r="D128" t="s">
-        <v>8</v>
-      </c>
-      <c r="E128" t="s">
-        <v>10</v>
-      </c>
-      <c r="F128" t="s">
+      <c r="H128" t="s">
         <v>15</v>
       </c>
-      <c r="G128" t="s">
-        <v>16</v>
-      </c>
-      <c r="H128" t="s">
-        <v>17</v>
-      </c>
       <c r="I128" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B129">
         <v>1</v>
       </c>
       <c r="C129" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D129" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E129" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G129" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H129" t="s">
         <v>1</v>
@@ -2566,45 +2566,45 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B130">
         <v>7.4800364500000001</v>
       </c>
       <c r="C130" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D130" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E130" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G130" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H130" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B131">
         <v>1.06382979</v>
       </c>
       <c r="C131" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D131" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E131" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G131" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H131" t="s">
         <v>1</v>
@@ -2612,117 +2612,117 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B132">
         <v>2.7014630000000001E-2</v>
       </c>
       <c r="C132" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D132" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E132" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G132" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H132" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B133">
         <v>-2.7014630000000001E-2</v>
       </c>
       <c r="C133" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D133" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E133" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G133" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H133" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B134">
         <v>4.3599999999999999E-7</v>
       </c>
       <c r="C134" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D134" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E134" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G134" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H134" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B135">
         <v>-1.9630400000000001E-3</v>
       </c>
       <c r="C135" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D135" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E135" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G135" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H135" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B136">
         <v>6.1099999999999994E-5</v>
       </c>
       <c r="C136" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D136" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E136" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G136" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H136" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.2">
@@ -2730,12 +2730,12 @@
         <v>2</v>
       </c>
       <c r="B138" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -2743,85 +2743,85 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B141" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B142" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B143" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
+        <v>11</v>
+      </c>
+      <c r="B145" t="s">
+        <v>12</v>
+      </c>
+      <c r="C145" t="s">
+        <v>5</v>
+      </c>
+      <c r="D145" t="s">
+        <v>6</v>
+      </c>
+      <c r="E145" t="s">
+        <v>8</v>
+      </c>
+      <c r="F145" t="s">
         <v>13</v>
       </c>
-      <c r="B145" t="s">
+      <c r="G145" t="s">
         <v>14</v>
       </c>
-      <c r="C145" t="s">
-        <v>6</v>
-      </c>
-      <c r="D145" t="s">
-        <v>8</v>
-      </c>
-      <c r="E145" t="s">
-        <v>10</v>
-      </c>
-      <c r="F145" t="s">
+      <c r="H145" t="s">
         <v>15</v>
       </c>
-      <c r="G145" t="s">
-        <v>16</v>
-      </c>
-      <c r="H145" t="s">
-        <v>17</v>
-      </c>
       <c r="I145" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B146">
         <v>1</v>
       </c>
       <c r="C146" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D146" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E146" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G146" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H146" t="s">
         <v>1</v>
@@ -2829,45 +2829,45 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B147">
         <v>5.3109436399999996</v>
       </c>
       <c r="C147" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D147" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E147" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G147" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H147" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B148">
         <v>1.06382979</v>
       </c>
       <c r="C148" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D148" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E148" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G148" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H148" t="s">
         <v>1</v>
@@ -2875,117 +2875,117 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B149">
         <v>2.8724590000000001E-2</v>
       </c>
       <c r="C149" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D149" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E149" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G149" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H149" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B150">
         <v>-2.8724590000000001E-2</v>
       </c>
       <c r="C150" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D150" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E150" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G150" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H150" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B151">
         <v>4.6400000000000003E-7</v>
       </c>
       <c r="C151" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D151" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E151" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G151" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H151" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B152">
         <v>-2.0872999999999998E-3</v>
       </c>
       <c r="C152" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D152" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E152" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G152" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H152" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B153">
         <v>6.4999999999999994E-5</v>
       </c>
       <c r="C153" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D153" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E153" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G153" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H153" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.2">
@@ -2993,12 +2993,12 @@
         <v>2</v>
       </c>
       <c r="B155" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -3006,85 +3006,85 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B158" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B159" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B160" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
+        <v>11</v>
+      </c>
+      <c r="B162" t="s">
+        <v>12</v>
+      </c>
+      <c r="C162" t="s">
+        <v>5</v>
+      </c>
+      <c r="D162" t="s">
+        <v>6</v>
+      </c>
+      <c r="E162" t="s">
+        <v>8</v>
+      </c>
+      <c r="F162" t="s">
         <v>13</v>
       </c>
-      <c r="B162" t="s">
+      <c r="G162" t="s">
         <v>14</v>
       </c>
-      <c r="C162" t="s">
-        <v>6</v>
-      </c>
-      <c r="D162" t="s">
-        <v>8</v>
-      </c>
-      <c r="E162" t="s">
-        <v>10</v>
-      </c>
-      <c r="F162" t="s">
+      <c r="H162" t="s">
         <v>15</v>
       </c>
-      <c r="G162" t="s">
-        <v>16</v>
-      </c>
-      <c r="H162" t="s">
-        <v>17</v>
-      </c>
       <c r="I162" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B163">
         <v>1</v>
       </c>
       <c r="C163" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D163" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E163" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G163" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H163" t="s">
         <v>1</v>
@@ -3092,45 +3092,45 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B164">
         <v>4.9234647999999996</v>
       </c>
       <c r="C164" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D164" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E164" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G164" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H164" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B165">
         <v>1.06382979</v>
       </c>
       <c r="C165" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D165" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E165" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G165" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H165" t="s">
         <v>1</v>
@@ -3138,117 +3138,117 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B166">
         <v>2.9280609999999999E-2</v>
       </c>
       <c r="C166" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D166" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E166" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G166" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H166" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B167">
         <v>-2.9280609999999999E-2</v>
       </c>
       <c r="C167" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D167" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E167" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G167" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H167" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B168">
         <v>4.7300000000000001E-7</v>
       </c>
       <c r="C168" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D168" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E168" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G168" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H168" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B169">
         <v>-2.1277000000000002E-3</v>
       </c>
       <c r="C169" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D169" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E169" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G169" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H169" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B170">
         <v>6.6199999999999996E-5</v>
       </c>
       <c r="C170" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D170" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E170" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G170" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H170" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.2">
@@ -3256,12 +3256,12 @@
         <v>2</v>
       </c>
       <c r="B172" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -3269,85 +3269,85 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B175" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B176" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B177" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
+        <v>11</v>
+      </c>
+      <c r="B179" t="s">
+        <v>12</v>
+      </c>
+      <c r="C179" t="s">
+        <v>5</v>
+      </c>
+      <c r="D179" t="s">
+        <v>6</v>
+      </c>
+      <c r="E179" t="s">
+        <v>8</v>
+      </c>
+      <c r="F179" t="s">
         <v>13</v>
       </c>
-      <c r="B179" t="s">
+      <c r="G179" t="s">
         <v>14</v>
       </c>
-      <c r="C179" t="s">
-        <v>6</v>
-      </c>
-      <c r="D179" t="s">
-        <v>8</v>
-      </c>
-      <c r="E179" t="s">
-        <v>10</v>
-      </c>
-      <c r="F179" t="s">
+      <c r="H179" t="s">
         <v>15</v>
       </c>
-      <c r="G179" t="s">
-        <v>16</v>
-      </c>
-      <c r="H179" t="s">
-        <v>17</v>
-      </c>
       <c r="I179" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B180">
         <v>1</v>
       </c>
       <c r="C180" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D180" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E180" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G180" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H180" t="s">
         <v>1</v>
@@ -3355,45 +3355,45 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B181">
         <v>4.5095973899999997</v>
       </c>
       <c r="C181" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D181" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E181" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G181" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H181" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B182">
         <v>1.06382979</v>
       </c>
       <c r="C182" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D182" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E182" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G182" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H182" t="s">
         <v>1</v>
@@ -3401,117 +3401,117 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B183">
         <v>3.0056340000000001E-2</v>
       </c>
       <c r="C183" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D183" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G183" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H183" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B184">
         <v>-3.0056340000000001E-2</v>
       </c>
       <c r="C184" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D184" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E184" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G184" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H184" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B185">
         <v>4.8500000000000002E-7</v>
       </c>
       <c r="C185" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D185" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E185" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G185" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H185" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B186">
         <v>-2.1840700000000002E-3</v>
       </c>
       <c r="C186" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D186" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E186" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G186" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H186" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B187">
         <v>6.7999999999999999E-5</v>
       </c>
       <c r="C187" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D187" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E187" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G187" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H187" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.2">
@@ -3519,12 +3519,12 @@
         <v>2</v>
       </c>
       <c r="B189" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -3532,85 +3532,85 @@
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B192" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B193" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B194" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
+        <v>11</v>
+      </c>
+      <c r="B196" t="s">
+        <v>12</v>
+      </c>
+      <c r="C196" t="s">
+        <v>5</v>
+      </c>
+      <c r="D196" t="s">
+        <v>6</v>
+      </c>
+      <c r="E196" t="s">
+        <v>8</v>
+      </c>
+      <c r="F196" t="s">
         <v>13</v>
       </c>
-      <c r="B196" t="s">
+      <c r="G196" t="s">
         <v>14</v>
       </c>
-      <c r="C196" t="s">
-        <v>6</v>
-      </c>
-      <c r="D196" t="s">
-        <v>8</v>
-      </c>
-      <c r="E196" t="s">
-        <v>10</v>
-      </c>
-      <c r="F196" t="s">
+      <c r="H196" t="s">
         <v>15</v>
       </c>
-      <c r="G196" t="s">
-        <v>16</v>
-      </c>
-      <c r="H196" t="s">
-        <v>17</v>
-      </c>
       <c r="I196" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B197">
         <v>1</v>
       </c>
       <c r="C197" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D197" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E197" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G197" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H197" t="s">
         <v>1</v>
@@ -3618,45 +3618,45 @@
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B198">
         <v>3.87762355</v>
       </c>
       <c r="C198" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D198" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E198" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G198" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H198" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B199">
         <v>1.0416666699999999</v>
       </c>
       <c r="C199" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D199" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E199" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G199" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H199" t="s">
         <v>1</v>
@@ -3664,117 +3664,117 @@
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B200">
         <v>2.4965629999999999E-2</v>
       </c>
       <c r="C200" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D200" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E200" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G200" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H200" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B201">
         <v>-2.4965629999999999E-2</v>
       </c>
       <c r="C201" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D201" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E201" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G201" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H201" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B202">
         <v>4.03E-7</v>
       </c>
       <c r="C202" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D202" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E202" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G202" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H202" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B203">
         <v>-1.8141500000000001E-3</v>
       </c>
       <c r="C203" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D203" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E203" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G203" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H203" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B204">
         <v>5.6499999999999998E-5</v>
       </c>
       <c r="C204" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D204" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E204" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G204" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H204" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.2">
@@ -3782,12 +3782,12 @@
         <v>2</v>
       </c>
       <c r="B206" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -3795,85 +3795,85 @@
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B209" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B210" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B211" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
+        <v>11</v>
+      </c>
+      <c r="B213" t="s">
+        <v>12</v>
+      </c>
+      <c r="C213" t="s">
+        <v>5</v>
+      </c>
+      <c r="D213" t="s">
+        <v>6</v>
+      </c>
+      <c r="E213" t="s">
+        <v>8</v>
+      </c>
+      <c r="F213" t="s">
         <v>13</v>
       </c>
-      <c r="B213" t="s">
+      <c r="G213" t="s">
         <v>14</v>
       </c>
-      <c r="C213" t="s">
-        <v>6</v>
-      </c>
-      <c r="D213" t="s">
-        <v>8</v>
-      </c>
-      <c r="E213" t="s">
-        <v>10</v>
-      </c>
-      <c r="F213" t="s">
+      <c r="H213" t="s">
         <v>15</v>
       </c>
-      <c r="G213" t="s">
-        <v>16</v>
-      </c>
-      <c r="H213" t="s">
-        <v>17</v>
-      </c>
       <c r="I213" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B214">
         <v>1</v>
       </c>
       <c r="C214" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D214" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E214" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G214" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H214" t="s">
         <v>1</v>
@@ -3881,45 +3881,45 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B215">
         <v>12.272039400000001</v>
       </c>
       <c r="C215" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D215" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E215" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G215" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H215" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B216">
         <v>1.0989011</v>
       </c>
       <c r="C216" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D216" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E216" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G216" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H216" t="s">
         <v>1</v>
@@ -3927,117 +3927,117 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B217">
         <v>2.6337369999999999E-2</v>
       </c>
       <c r="C217" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D217" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E217" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G217" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H217" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B218">
         <v>-2.6337369999999999E-2</v>
       </c>
       <c r="C218" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D218" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E218" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G218" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H218" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B219">
         <v>4.2500000000000001E-7</v>
       </c>
       <c r="C219" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D219" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E219" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G219" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H219" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B220">
         <v>-1.91383E-3</v>
       </c>
       <c r="C220" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D220" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E220" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G220" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H220" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B221">
         <v>5.9599999999999999E-5</v>
       </c>
       <c r="C221" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D221" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E221" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G221" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H221" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.2">
@@ -4045,12 +4045,12 @@
         <v>2</v>
       </c>
       <c r="B223" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -4058,85 +4058,85 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B226" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B227" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B228" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
+        <v>11</v>
+      </c>
+      <c r="B230" t="s">
+        <v>12</v>
+      </c>
+      <c r="C230" t="s">
+        <v>5</v>
+      </c>
+      <c r="D230" t="s">
+        <v>6</v>
+      </c>
+      <c r="E230" t="s">
+        <v>8</v>
+      </c>
+      <c r="F230" t="s">
         <v>13</v>
       </c>
-      <c r="B230" t="s">
+      <c r="G230" t="s">
         <v>14</v>
       </c>
-      <c r="C230" t="s">
-        <v>6</v>
-      </c>
-      <c r="D230" t="s">
-        <v>8</v>
-      </c>
-      <c r="E230" t="s">
-        <v>10</v>
-      </c>
-      <c r="F230" t="s">
+      <c r="H230" t="s">
         <v>15</v>
       </c>
-      <c r="G230" t="s">
-        <v>16</v>
-      </c>
-      <c r="H230" t="s">
-        <v>17</v>
-      </c>
       <c r="I230" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B231">
         <v>1</v>
       </c>
       <c r="C231" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D231" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E231" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G231" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H231" t="s">
         <v>1</v>
@@ -4144,45 +4144,45 @@
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B232">
         <v>11.1186338</v>
       </c>
       <c r="C232" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D232" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E232" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G232" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H232" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B233">
         <v>1.07526882</v>
       </c>
       <c r="C233" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D233" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E233" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G233" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H233" t="s">
         <v>1</v>
@@ -4190,117 +4190,117 @@
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B234">
         <v>2.5770970000000001E-2</v>
       </c>
       <c r="C234" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D234" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E234" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G234" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H234" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B235">
         <v>-2.5770970000000001E-2</v>
       </c>
       <c r="C235" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D235" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E235" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G235" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H235" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B236">
         <v>4.1600000000000002E-7</v>
       </c>
       <c r="C236" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D236" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E236" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G236" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H236" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B237">
         <v>-1.8726700000000001E-3</v>
       </c>
       <c r="C237" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D237" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E237" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G237" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H237" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B238">
         <v>5.8300000000000001E-5</v>
       </c>
       <c r="C238" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D238" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E238" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G238" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H238" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.2">
@@ -4308,12 +4308,12 @@
         <v>2</v>
       </c>
       <c r="B240" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B241">
         <v>1</v>
@@ -4321,85 +4321,85 @@
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B243" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B244" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B245" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
+        <v>11</v>
+      </c>
+      <c r="B247" t="s">
+        <v>12</v>
+      </c>
+      <c r="C247" t="s">
+        <v>5</v>
+      </c>
+      <c r="D247" t="s">
+        <v>6</v>
+      </c>
+      <c r="E247" t="s">
+        <v>8</v>
+      </c>
+      <c r="F247" t="s">
         <v>13</v>
       </c>
-      <c r="B247" t="s">
+      <c r="G247" t="s">
         <v>14</v>
       </c>
-      <c r="C247" t="s">
-        <v>6</v>
-      </c>
-      <c r="D247" t="s">
-        <v>8</v>
-      </c>
-      <c r="E247" t="s">
-        <v>10</v>
-      </c>
-      <c r="F247" t="s">
+      <c r="H247" t="s">
         <v>15</v>
       </c>
-      <c r="G247" t="s">
-        <v>16</v>
-      </c>
-      <c r="H247" t="s">
-        <v>17</v>
-      </c>
       <c r="I247" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B248">
         <v>1</v>
       </c>
       <c r="C248" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D248" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E248" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G248" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H248" t="s">
         <v>1</v>
@@ -4407,45 +4407,45 @@
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B249">
         <v>8.4602695600000004</v>
       </c>
       <c r="C249" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D249" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E249" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G249" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H249" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B250">
         <v>1.1363636399999999</v>
       </c>
       <c r="C250" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D250" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E250" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G250" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H250" t="s">
         <v>1</v>
@@ -4453,117 +4453,117 @@
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B251">
         <v>2.7235229999999999E-2</v>
       </c>
       <c r="C251" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D251" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E251" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G251" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H251" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B252">
         <v>-2.7235229999999999E-2</v>
       </c>
       <c r="C252" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D252" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E252" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G252" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H252" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B253">
         <v>4.4000000000000002E-7</v>
       </c>
       <c r="C253" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D253" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E253" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G253" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H253" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B254">
         <v>-1.9790699999999999E-3</v>
       </c>
       <c r="C254" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D254" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E254" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G254" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H254" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B255">
         <v>6.1600000000000007E-5</v>
       </c>
       <c r="C255" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D255" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E255" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G255" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H255" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.2">
@@ -4571,12 +4571,12 @@
         <v>2</v>
       </c>
       <c r="B257" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B258">
         <v>1</v>
@@ -4584,85 +4584,85 @@
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B260" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B261" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B262" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
+        <v>11</v>
+      </c>
+      <c r="B264" t="s">
+        <v>12</v>
+      </c>
+      <c r="C264" t="s">
+        <v>5</v>
+      </c>
+      <c r="D264" t="s">
+        <v>6</v>
+      </c>
+      <c r="E264" t="s">
+        <v>8</v>
+      </c>
+      <c r="F264" t="s">
         <v>13</v>
       </c>
-      <c r="B264" t="s">
+      <c r="G264" t="s">
         <v>14</v>
       </c>
-      <c r="C264" t="s">
-        <v>6</v>
-      </c>
-      <c r="D264" t="s">
-        <v>8</v>
-      </c>
-      <c r="E264" t="s">
-        <v>10</v>
-      </c>
-      <c r="F264" t="s">
+      <c r="H264" t="s">
         <v>15</v>
       </c>
-      <c r="G264" t="s">
-        <v>16</v>
-      </c>
-      <c r="H264" t="s">
-        <v>17</v>
-      </c>
       <c r="I264" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B265">
         <v>1</v>
       </c>
       <c r="C265" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D265" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E265" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G265" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H265" t="s">
         <v>1</v>
@@ -4670,140 +4670,140 @@
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B266">
         <v>15.5299145</v>
       </c>
       <c r="C266" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D266" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E266" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G266" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H266" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B267">
         <v>3.3516480000000001E-2</v>
       </c>
       <c r="C267" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D267" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E267" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G267" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H267" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B268">
         <v>-3.3516480000000001E-2</v>
       </c>
       <c r="C268" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D268" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E268" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G268" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H268" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B269">
         <v>5.4099999999999999E-7</v>
       </c>
       <c r="C269" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D269" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E269" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G269" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H269" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B270">
         <v>-2.4355100000000001E-3</v>
       </c>
       <c r="C270" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D270" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E270" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G270" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H270" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B271">
         <v>7.5799999999999999E-5</v>
       </c>
       <c r="C271" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D271" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E271" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G271" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H271" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.2">
@@ -4811,12 +4811,12 @@
         <v>2</v>
       </c>
       <c r="B273" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B274">
         <v>1</v>
@@ -4824,85 +4824,85 @@
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B276" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B277" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B278" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
+        <v>11</v>
+      </c>
+      <c r="B280" t="s">
+        <v>12</v>
+      </c>
+      <c r="C280" t="s">
+        <v>5</v>
+      </c>
+      <c r="D280" t="s">
+        <v>6</v>
+      </c>
+      <c r="E280" t="s">
+        <v>8</v>
+      </c>
+      <c r="F280" t="s">
         <v>13</v>
       </c>
-      <c r="B280" t="s">
+      <c r="G280" t="s">
         <v>14</v>
       </c>
-      <c r="C280" t="s">
-        <v>6</v>
-      </c>
-      <c r="D280" t="s">
-        <v>8</v>
-      </c>
-      <c r="E280" t="s">
-        <v>10</v>
-      </c>
-      <c r="F280" t="s">
+      <c r="H280" t="s">
         <v>15</v>
       </c>
-      <c r="G280" t="s">
-        <v>16</v>
-      </c>
-      <c r="H280" t="s">
-        <v>17</v>
-      </c>
       <c r="I280" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B281">
         <v>1</v>
       </c>
       <c r="C281" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D281" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E281" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G281" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H281" t="s">
         <v>1</v>
@@ -4910,140 +4910,140 @@
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B282">
         <v>8.3186813199999996</v>
       </c>
       <c r="C282" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D282" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E282" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G282" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H282" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B283">
         <v>3.3516480000000001E-2</v>
       </c>
       <c r="C283" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D283" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E283" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G283" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H283" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B284">
         <v>-3.3516480000000001E-2</v>
       </c>
       <c r="C284" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D284" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E284" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G284" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H284" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B285">
         <v>5.4099999999999999E-7</v>
       </c>
       <c r="C285" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D285" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E285" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G285" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H285" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B286">
         <v>-2.4355100000000001E-3</v>
       </c>
       <c r="C286" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D286" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E286" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G286" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H286" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B287">
         <v>7.5799999999999999E-5</v>
       </c>
       <c r="C287" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D287" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E287" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G287" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H287" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.2">
@@ -5051,12 +5051,12 @@
         <v>2</v>
       </c>
       <c r="B289" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B290">
         <v>1</v>
@@ -5064,85 +5064,85 @@
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B292" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B293" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B294" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
+        <v>11</v>
+      </c>
+      <c r="B296" t="s">
+        <v>12</v>
+      </c>
+      <c r="C296" t="s">
+        <v>5</v>
+      </c>
+      <c r="D296" t="s">
+        <v>6</v>
+      </c>
+      <c r="E296" t="s">
+        <v>8</v>
+      </c>
+      <c r="F296" t="s">
         <v>13</v>
       </c>
-      <c r="B296" t="s">
+      <c r="G296" t="s">
         <v>14</v>
       </c>
-      <c r="C296" t="s">
-        <v>6</v>
-      </c>
-      <c r="D296" t="s">
-        <v>8</v>
-      </c>
-      <c r="E296" t="s">
-        <v>10</v>
-      </c>
-      <c r="F296" t="s">
+      <c r="H296" t="s">
         <v>15</v>
       </c>
-      <c r="G296" t="s">
-        <v>16</v>
-      </c>
-      <c r="H296" t="s">
-        <v>17</v>
-      </c>
       <c r="I296" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B297">
         <v>1</v>
       </c>
       <c r="C297" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D297" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E297" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G297" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H297" t="s">
         <v>1</v>
@@ -5150,140 +5150,140 @@
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B298">
         <v>1.8791208800000001</v>
       </c>
       <c r="C298" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D298" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E298" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G298" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H298" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B299">
         <v>3.3516480000000001E-2</v>
       </c>
       <c r="C299" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D299" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E299" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G299" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H299" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B300">
         <v>-3.3516480000000001E-2</v>
       </c>
       <c r="C300" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D300" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E300" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G300" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H300" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B301">
         <v>5.4099999999999999E-7</v>
       </c>
       <c r="C301" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D301" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E301" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G301" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H301" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B302">
         <v>-2.4355100000000001E-3</v>
       </c>
       <c r="C302" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D302" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E302" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G302" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H302" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B303">
         <v>7.5799999999999999E-5</v>
       </c>
       <c r="C303" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D303" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E303" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G303" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H303" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.2">
@@ -5291,12 +5291,12 @@
         <v>2</v>
       </c>
       <c r="B305" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B306">
         <v>1</v>
@@ -5304,85 +5304,85 @@
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B308" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B309" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B310" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
+        <v>11</v>
+      </c>
+      <c r="B312" t="s">
+        <v>12</v>
+      </c>
+      <c r="C312" t="s">
+        <v>5</v>
+      </c>
+      <c r="D312" t="s">
+        <v>6</v>
+      </c>
+      <c r="E312" t="s">
+        <v>8</v>
+      </c>
+      <c r="F312" t="s">
         <v>13</v>
       </c>
-      <c r="B312" t="s">
+      <c r="G312" t="s">
         <v>14</v>
       </c>
-      <c r="C312" t="s">
-        <v>6</v>
-      </c>
-      <c r="D312" t="s">
-        <v>8</v>
-      </c>
-      <c r="E312" t="s">
-        <v>10</v>
-      </c>
-      <c r="F312" t="s">
+      <c r="H312" t="s">
         <v>15</v>
       </c>
-      <c r="G312" t="s">
-        <v>16</v>
-      </c>
-      <c r="H312" t="s">
-        <v>17</v>
-      </c>
       <c r="I312" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B313">
         <v>1</v>
       </c>
       <c r="C313" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D313" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E313" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G313" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H313" t="s">
         <v>1</v>
@@ -5390,45 +5390,45 @@
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B314">
         <v>1.2</v>
       </c>
       <c r="C314" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D314" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E314" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G314" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H314" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="B315">
         <v>10.8</v>
       </c>
       <c r="C315" t="s">
-        <v>7</v>
+        <v>81</v>
       </c>
       <c r="D315" t="s">
+        <v>7</v>
+      </c>
+      <c r="E315" t="s">
         <v>9</v>
       </c>
-      <c r="E315" t="s">
-        <v>11</v>
-      </c>
       <c r="G315" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H315" t="s">
         <v>1</v>
@@ -5436,186 +5436,186 @@
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B316">
         <v>3.3516480000000001E-2</v>
       </c>
       <c r="C316" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D316" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E316" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G316" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H316" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B317">
         <v>-3.3516480000000001E-2</v>
       </c>
       <c r="C317" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D317" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E317" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G317" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H317" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B318">
         <v>5.4099999999999999E-7</v>
       </c>
       <c r="C318" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D318" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E318" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G318" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H318" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B319">
         <v>-2.4355100000000001E-3</v>
       </c>
       <c r="C319" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D319" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E319" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G319" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H319" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B320">
         <v>7.5799999999999999E-5</v>
       </c>
       <c r="C320" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D320" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E320" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G320" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H320" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B321">
         <v>0.5</v>
       </c>
       <c r="C321" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D321" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E321" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G321" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H321" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A322" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B322">
         <v>-4.4999999999999999E-4</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D322" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E322" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G322" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H322" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B323">
         <v>5.0000000000000002E-5</v>
       </c>
       <c r="D323" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E323" t="s">
+        <v>47</v>
+      </c>
+      <c r="F323" t="s">
         <v>49</v>
       </c>
-      <c r="F323" t="s">
+      <c r="G323" t="s">
+        <v>50</v>
+      </c>
+      <c r="H323" t="s">
         <v>51</v>
-      </c>
-      <c r="G323" t="s">
-        <v>52</v>
-      </c>
-      <c r="H323" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.2">
@@ -5623,12 +5623,12 @@
         <v>2</v>
       </c>
       <c r="B325" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B326">
         <v>1</v>
@@ -5636,85 +5636,85 @@
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B328" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B329" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B330" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
+        <v>11</v>
+      </c>
+      <c r="B332" t="s">
+        <v>12</v>
+      </c>
+      <c r="C332" t="s">
+        <v>5</v>
+      </c>
+      <c r="D332" t="s">
+        <v>6</v>
+      </c>
+      <c r="E332" t="s">
+        <v>8</v>
+      </c>
+      <c r="F332" t="s">
         <v>13</v>
       </c>
-      <c r="B332" t="s">
+      <c r="G332" t="s">
         <v>14</v>
       </c>
-      <c r="C332" t="s">
-        <v>6</v>
-      </c>
-      <c r="D332" t="s">
-        <v>8</v>
-      </c>
-      <c r="E332" t="s">
-        <v>10</v>
-      </c>
-      <c r="F332" t="s">
+      <c r="H332" t="s">
         <v>15</v>
       </c>
-      <c r="G332" t="s">
-        <v>16</v>
-      </c>
-      <c r="H332" t="s">
-        <v>17</v>
-      </c>
       <c r="I332" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B333">
         <v>1</v>
       </c>
       <c r="C333" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D333" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E333" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G333" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H333" t="s">
         <v>1</v>
@@ -5722,45 +5722,45 @@
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B334">
         <v>1.75</v>
       </c>
       <c r="C334" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D334" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E334" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G334" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H334" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="B335">
         <v>8.4499999999999993</v>
       </c>
       <c r="C335" t="s">
-        <v>7</v>
+        <v>81</v>
       </c>
       <c r="D335" t="s">
+        <v>7</v>
+      </c>
+      <c r="E335" t="s">
         <v>9</v>
       </c>
-      <c r="E335" t="s">
-        <v>11</v>
-      </c>
       <c r="G335" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H335" t="s">
         <v>1</v>
@@ -5768,209 +5768,209 @@
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B336">
         <v>0.01</v>
       </c>
       <c r="C336" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D336" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E336" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G336" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H336" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B337">
         <v>3.3516480000000001E-2</v>
       </c>
       <c r="C337" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D337" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E337" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G337" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H337" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B338">
         <v>-3.3516480000000001E-2</v>
       </c>
       <c r="C338" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D338" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E338" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G338" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H338" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B339">
         <v>5.4099999999999999E-7</v>
       </c>
       <c r="C339" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D339" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E339" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G339" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H339" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B340">
         <v>-2.4355100000000001E-3</v>
       </c>
       <c r="C340" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D340" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E340" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G340" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H340" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B341">
         <v>7.5799999999999999E-5</v>
       </c>
       <c r="C341" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D341" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E341" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G341" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H341" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B342">
         <v>8</v>
       </c>
       <c r="C342" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D342" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E342" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G342" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H342" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A343" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B343">
         <v>-7.1999999999999998E-3</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D343" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E343" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G343" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H343" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B344">
         <v>8.0000000000000004E-4</v>
       </c>
       <c r="D344" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E344" t="s">
+        <v>47</v>
+      </c>
+      <c r="F344" t="s">
         <v>49</v>
       </c>
-      <c r="F344" t="s">
+      <c r="G344" t="s">
+        <v>50</v>
+      </c>
+      <c r="H344" t="s">
         <v>51</v>
-      </c>
-      <c r="G344" t="s">
-        <v>52</v>
-      </c>
-      <c r="H344" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/weaving/inventory-brightway.xlsx
+++ b/datasets/weaving/inventory-brightway.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vincentcarrieres/carbonfact/lca/lca/notebooks/science/Carbonfact database/Weaving/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE19F7C-6B81-614C-8BE5-0217CF69FCC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B0F4C8E-3E25-224B-B573-9AF39E17026C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4540" yWindow="-21000" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16940" yWindow="-21000" windowWidth="16300" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -1129,7 +1129,7 @@
         <v>48</v>
       </c>
       <c r="B34">
-        <v>1.008554631</v>
+        <v>1.0085546309999999E-3</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
